--- a/smartfridge_budget.xlsx
+++ b/smartfridge_budget.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget détaillé" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,117 +448,586 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Prototype matériel</t>
+          <t>R&amp;D produit</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Frigo modifié + caméras + module IA embarqué</t>
+          <t>Ingénierie IoT / mécanique intégration caméra</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1100</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Développement logiciel</t>
+          <t>R&amp;D produit</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>App mobile, backend FastAPI, intégration Drive</t>
+          <t>Ingénierie vision / IA (détection, suivi quantité)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ressources humaines (IA / IoT / Mobile / Backend)</t>
+          <t>R&amp;D produit</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1 mois de travail cumulé des rôles clés</t>
+          <t>Gestion projet / Product Owner</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Infra Cloud (hébergement API / DB)</t>
+          <t>R&amp;D produit</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Serveur OVH/AWS + stockage données 1 an</t>
+          <t>Frigos base (x2) pour tests</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tests terrain / panels utilisateurs</t>
+          <t>R&amp;D produit</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Séances de tests en conditions réelles</t>
+          <t>Outillage / adaptation physique proto</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Communication / gouvernance projet</t>
+          <t>Sous-total R&amp;D produit</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Réunions projet, doc, pilotage PO</t>
+          <t>SOUS-TOTAL R&amp;D produit</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marge imprévus (10%)</t>
+          <t>Électronique / IA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Buffer sécurité budget matériel / délai fournisseur</t>
+          <t>Caméras internes HD x3</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>620</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>Électronique / IA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Module IA embarqué (Jetson / Raspberry Pi)</t>
+        </is>
+      </c>
       <c r="C9" t="n">
-        <v>6820</v>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Électronique / IA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Boîtier étanche / câblage interne</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Électronique / IA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Capteurs additionnels (ouverture porte / température)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sous-total Électronique / IA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SOUS-TOTAL ÉLECTRONIQUE / IA</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Logiciel</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dev IA embarquée (inférence locale TensorRT)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Logiciel</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dev firmware frigo → cloud sécurisé</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Logiciel</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dev backend FastAPI + PostgreSQL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Logiciel</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dev microservice intégration Drive</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Logiciel</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dev app mobile React Native</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Logiciel</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Recette / QA logiciel</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sous-total Logiciel</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SOUS-TOTAL LOGICIEL</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Conformité / Légal</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Audit RGPD / privacy by design</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Conformité / Légal</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pré-étude conformité CE / électrique</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Conformité / Légal</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Audit sécurité IoT / chiffrement</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sous-total Conformité / Légal</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SOUS-TOTAL CONFORMITÉ</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Industrialisation</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Design industriel / intégration propre hardware</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Industrialisation</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Prototype pré-série (5-10 unités de démo)</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Industrialisation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Packaging / notice / étiquetage conformité</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sous-total Industrialisation</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SOUS-TOTAL INDUSTRIALISATION</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Logistique / Distribution</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Stockage court terme / entrepôt</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Logistique / Distribution</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Livraison + installation familles test</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Logistique / Distribution</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SAV pilote (remplacement / visite tech)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sous-total Logistique / Distribution</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SOUS-TOTAL LOGISTIQUE</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Marketing / Go-to-Market</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Vidéo démo + visuels produit</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Marketing / Go-to-Market</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Message commercial / positionnement</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Marketing / Go-to-Market</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Formation vendeur partenaire Drive</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sous-total Marketing / Go-to-Market</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SOUS-TOTAL MARKETING</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Exploitation / Support</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Hébergement cloud / monitoring 12 mois</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Exploitation / Support</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Maintenance logicielle OTA</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Exploitation / Support</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Support utilisateur pilote</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sous-total Exploitation / Support</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SOUS-TOTAL EXPLOITATION</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TOTAL PROJET</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>TOTAL PROJET</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>43280</v>
       </c>
     </row>
   </sheetData>
